--- a/Result/profitability/2327.xlsx
+++ b/Result/profitability/2327.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>6.1725</v>
+        <v>5.375</v>
       </c>
       <c r="N2" t="n">
-        <v>34.31</v>
+        <v>34.72</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.32</v>
       </c>
       <c r="M3" t="n">
-        <v>4.84125</v>
+        <v>4.5025</v>
       </c>
       <c r="N3" t="n">
-        <v>32.58375</v>
+        <v>33.25</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.66</v>
       </c>
       <c r="M4" t="n">
-        <v>4.01125</v>
+        <v>3.23875</v>
       </c>
       <c r="N4" t="n">
-        <v>31.03</v>
+        <v>31.3875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.53125</v>
+        <v>1.8875</v>
       </c>
       <c r="N5" t="n">
-        <v>28.20625</v>
+        <v>28.57375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.21</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2875</v>
+        <v>1.47375</v>
       </c>
       <c r="N6" t="n">
-        <v>24.58</v>
+        <v>24.86875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9075000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>22.73375</v>
+        <v>22.88375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.23</v>
       </c>
       <c r="M8" t="n">
-        <v>0.525</v>
+        <v>0.61125</v>
       </c>
       <c r="N8" t="n">
-        <v>20.965</v>
+        <v>21.015</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>44456</v>
+      </c>
+      <c r="D75" t="n">
+        <v>27340</v>
+      </c>
+      <c r="E75" t="n">
+        <v>17116</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>11749</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>26.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>474</v>
+      </c>
+      <c r="J75" t="n">
+        <v>12222</v>
+      </c>
+      <c r="K75" t="n">
+        <v>9418</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="M75" t="n">
+        <v>6.7075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>36.21</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.176923076923077</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01049868766404205</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-5.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5287474332648872</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.939999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.08267716535433056</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
